--- a/sheets/대금율보/검수/여행을 떠나요.xlsx
+++ b/sheets/대금율보/검수/여행을 떠나요.xlsx
@@ -5197,24 +5197,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="85.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.43" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.43" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.43" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.43" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.43" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.43" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="M8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.43" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.43" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="M10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.43" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -5742,7 +5742,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.43" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.43" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.43" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
@@ -5919,7 +5919,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.43" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5962,7 +5962,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.43" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M16" s="27"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.43" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="M17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.43" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="M18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="63.43" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="63.43" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="25"/>
@@ -6179,7 +6179,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="63.43" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="63.43" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="26"/>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="63.43" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -6345,7 +6345,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="63.43" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="25"/>
@@ -6374,7 +6374,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="25"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="63.43" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="25"/>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="M25" s="25"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="63.43" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="26"/>
@@ -6438,6 +6438,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="47"/>
 </worksheet>
 </file>